--- a/hj/intergrated_test_tool/data/neimeng/监测站信息.xlsx
+++ b/hj/intergrated_test_tool/data/neimeng/监测站信息.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\python\script_tools\data\neimeng\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\git\tool\hj\intergrated_test_tool\data\neimeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0870EF16-0C7B-4D4A-A389-6DADD6296264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EDE315-A162-47F2-81A9-FE3CBD738581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>mfid</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,24 +51,90 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>锡林郭勒盟东乌旗站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15250001142004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.9693</t>
-  </si>
-  <si>
-    <t>45.5092</t>
-  </si>
-  <si>
-    <t>内蒙古自治区锡林郭勒盟老联通公司院基站</t>
-  </si>
-  <si>
-    <t>172.16.235.167</t>
+    <t>锡林格勒盟镶黄旗机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15250001122010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区锡林格勒盟镶黄旗新宝拉格机场</t>
+  </si>
+  <si>
+    <t>172.16.235.147</t>
+  </si>
+  <si>
+    <t>15260001122006</t>
+  </si>
+  <si>
+    <t>乌兰察布市罗家村联通站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区乌兰察布盟罗家村联通基站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.230.159</t>
+  </si>
+  <si>
+    <t>15060001122003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂尔多斯机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区鄂尔多斯市伊金霍洛机场管理集团</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.233.100</t>
+  </si>
+  <si>
+    <t>15290001120010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿拉善盟额济纳旗机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区阿拉善盟额济纳旗桃来机场办公楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.238.64</t>
+  </si>
+  <si>
+    <t>15280001122010</t>
+  </si>
+  <si>
+    <t>巴彦淖尔机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区巴彦淖尔机场职工宿舍楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.234.97</t>
+  </si>
+  <si>
+    <t>15290001122002</t>
+  </si>
+  <si>
+    <t>阿拉善盟阿右旗机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区阿拉善盟右旗机场办公楼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.238.67</t>
   </si>
 </sst>
 </file>
@@ -399,18 +465,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,24 +496,124 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2">
+        <v>113.749549</v>
+      </c>
+      <c r="D2">
+        <v>42.269164000000004</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>11</v>
+      </c>
+      <c r="C3">
+        <v>113.117768</v>
+      </c>
+      <c r="D3">
+        <v>41.084122000000001</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>109.86819300000001</v>
+      </c>
+      <c r="D4">
+        <v>39.495933000000001</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>100.997513</v>
+      </c>
+      <c r="D5">
+        <v>42.012017</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>107.739835</v>
+      </c>
+      <c r="D6">
+        <v>40.922080000000001</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
+        <v>101.54625</v>
+      </c>
+      <c r="D7">
+        <v>39.223269999999999</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/hj/intergrated_test_tool/data/neimeng/监测站信息.xlsx
+++ b/hj/intergrated_test_tool/data/neimeng/监测站信息.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20392"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\git\tool\hj\intergrated_test_tool\data\neimeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1EDE315-A162-47F2-81A9-FE3CBD738581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E92C848-EC0D-4731-9055-B210BFCA4712}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>mfid</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,90 +51,101 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>锡林格勒盟镶黄旗机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15250001122010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区锡林格勒盟镶黄旗新宝拉格机场</t>
-  </si>
-  <si>
-    <t>172.16.235.147</t>
-  </si>
-  <si>
-    <t>15260001122006</t>
-  </si>
-  <si>
-    <t>乌兰察布市罗家村联通站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区乌兰察布盟罗家村联通基站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>172.16.230.159</t>
-  </si>
-  <si>
-    <t>15060001122003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鄂尔多斯机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区鄂尔多斯市伊金霍洛机场管理集团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>172.16.233.100</t>
-  </si>
-  <si>
-    <t>15290001120010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿拉善盟额济纳旗机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区阿拉善盟额济纳旗桃来机场办公楼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>172.16.238.64</t>
-  </si>
-  <si>
-    <t>15280001122010</t>
-  </si>
-  <si>
-    <t>巴彦淖尔机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区巴彦淖尔机场职工宿舍楼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>172.16.234.97</t>
-  </si>
-  <si>
-    <t>15290001122002</t>
-  </si>
-  <si>
-    <t>阿拉善盟阿右旗机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内蒙古自治区阿拉善盟右旗机场办公楼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>172.16.238.67</t>
+    <t>15020000130181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包头九原小召湾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包头市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.228.181</t>
+  </si>
+  <si>
+    <t>15040000130127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤峰机场航空监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区赤峰市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.232.127</t>
+  </si>
+  <si>
+    <t>15250000130055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二连浩特机场升级监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锡林郭勒盟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.235.55</t>
+  </si>
+  <si>
+    <t>15030000130056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌海北站监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区乌海市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.229.56</t>
+  </si>
+  <si>
+    <t>15250000130050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锡林浩特机场升级监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.235.50</t>
+  </si>
+  <si>
+    <t>15220000130165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔山机场航空站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内蒙古自治区兴安盟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.237.165</t>
+  </si>
+  <si>
+    <t>15220000130170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌兰浩特机场航空站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>172.16.237.170</t>
   </si>
 </sst>
 </file>
@@ -465,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.75" style="1" customWidth="1"/>
@@ -498,16 +509,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
       <c r="C2">
-        <v>113.749549</v>
+        <v>109.941383</v>
       </c>
       <c r="D2">
-        <v>42.269164000000004</v>
+        <v>40.547241</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -524,10 +535,10 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>113.117768</v>
+        <v>118.83045199999999</v>
       </c>
       <c r="D3">
-        <v>41.084122000000001</v>
+        <v>42.187339999999999</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -544,10 +555,10 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>109.86819300000001</v>
+        <v>112.09929700000001</v>
       </c>
       <c r="D4">
-        <v>39.495933000000001</v>
+        <v>43.426414000000001</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -564,10 +575,10 @@
         <v>19</v>
       </c>
       <c r="C5">
-        <v>100.997513</v>
+        <v>106.775627</v>
       </c>
       <c r="D5">
-        <v>42.012017</v>
+        <v>39.790253</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -584,36 +595,56 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>107.739835</v>
+        <v>115.89971199999999</v>
       </c>
       <c r="D6">
-        <v>40.922080000000001</v>
+        <v>43.947482999999998</v>
       </c>
       <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
         <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7">
+        <v>119.923958</v>
+      </c>
+      <c r="D7">
+        <v>47.306870000000004</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="C7">
-        <v>101.54625</v>
-      </c>
-      <c r="D7">
-        <v>39.223269999999999</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8">
+        <v>122.00387600000001</v>
+      </c>
+      <c r="D8">
+        <v>46.191257</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
